--- a/notebooks/rda-experiments/runs/v10c-narrative/evaluation_results.xlsx
+++ b/notebooks/rda-experiments/runs/v10c-narrative/evaluation_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="152">
   <si>
     <t>fields in reference</t>
   </si>
@@ -155,6 +155,24 @@
     <t>dmp.dataset[2].type</t>
   </si>
   <si>
+    <t>dmp.dataset[3].dataset_id.identifier</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].dataset_id.type</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].personal_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].sensitive_data</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].title</t>
+  </si>
+  <si>
+    <t>dmp.dataset[3].type</t>
+  </si>
+  <si>
     <t>dmp.dmp_id.identifier</t>
   </si>
   <si>
@@ -230,15 +248,6 @@
     <t>dmp.dataset[3].metadata[0].language</t>
   </si>
   <si>
-    <t>dmp.dataset[3].personal_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].sensitive_data</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].title</t>
-  </si>
-  <si>
     <t>dmp.description</t>
   </si>
   <si>
@@ -263,6 +272,9 @@
     <t>Simulation code for controller development and testing</t>
   </si>
   <si>
+    <t>Software generated under the project</t>
+  </si>
+  <si>
     <t>eng</t>
   </si>
   <si>
@@ -275,6 +287,9 @@
     <t>planned</t>
   </si>
   <si>
+    <t>isPartOf</t>
+  </si>
+  <si>
     <t>data related to each of our proposed experiments</t>
   </si>
   <si>
@@ -284,6 +299,9 @@
     <t>simulation code for controller development and testing</t>
   </si>
   <si>
+    <t>videos of the experiments</t>
+  </si>
+  <si>
     <t>First, we will have data related to each of our proposed experiments. These will include the detailed protocols used for each experiment, the raw data collected from each experiment, and the experimental code used to collect those data. The relevant code will include both the data acquisition code, and the code for the controllers used in the experiment. Together, this information will be sufficient for recreating the circumstances of each data collection session.</t>
   </si>
   <si>
@@ -308,9 +326,6 @@
     <t>Select videos of the experiments will be distributed, with subject faces blurred so as to be unidentifiable.</t>
   </si>
   <si>
-    <t>videos of the experiments</t>
-  </si>
-  <si>
     <t>We will manage all scientific and technical content generated from this proposal. Our products will include 3 broad types of data.</t>
   </si>
   <si>
@@ -329,6 +344,9 @@
     <t>not in the reference</t>
   </si>
   <si>
+    <t>only 20% of the model's words are in the reference</t>
+  </si>
+  <si>
     <t>dmp.dataset[0].distribution[0].data_access</t>
   </si>
   <si>
@@ -380,39 +398,6 @@
     <t>dmp.dataset[1].metadata[0].metadata_standard_id[0].type</t>
   </si>
   <si>
-    <t>dmp.dataset[3].dataset_id.identifier</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].dataset_id.type</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].distribution[0].data_access</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].distribution[0].title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].distribution[0].host.title</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].distribution[0].host.url</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].distribution[0].license[0].license_ref</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].distribution[0].license[0].start_date</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].metadata[0].metadata_standard_id[0].identifier</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].metadata[0].metadata_standard_id[0].type</t>
-  </si>
-  <si>
-    <t>dmp.dataset[3].metadata[0].description</t>
-  </si>
-  <si>
     <t>dmp.dataset[2].distribution[0].data_access</t>
   </si>
   <si>
@@ -452,6 +437,9 @@
     <t>Specifically, we store all code necessary to recreate figures, tables, and other results reported in all published manuscripts. The proposed foundational developments will produce substantial simulation code for controller development and testing. These and the outputs relevant to all key findings will also be managed.</t>
   </si>
   <si>
+    <t>These and the outputs relevant to all key findings will also be managed.</t>
+  </si>
+  <si>
     <t>unknown</t>
   </si>
   <si>
@@ -464,9 +452,6 @@
     <t>empty where the reference has a value</t>
   </si>
   <si>
-    <t>dmp.dataset[3].type</t>
-  </si>
-  <si>
     <t>dmp.dataset[4].dataset_id.identifier</t>
   </si>
   <si>
@@ -489,9 +474,6 @@
   </si>
   <si>
     <t>Select videos of the experiments</t>
-  </si>
-  <si>
-    <t>Software generated under the project</t>
   </si>
 </sst>
 </file>
@@ -898,34 +880,34 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0.514</v>
+        <v>0.512</v>
       </c>
       <c r="H2">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="I2">
-        <v>0.45</v>
+        <v>0.495</v>
       </c>
       <c r="J2">
-        <v>0.3653846153846154</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="K2">
-        <v>0.3461538461538461</v>
+        <v>0.375</v>
       </c>
       <c r="L2">
-        <v>0.2884615384615384</v>
+        <v>0.2321428571428572</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -939,31 +921,31 @@
         <v>61</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>0.525</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H3">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="I3">
-        <v>0.5600000000000001</v>
+        <v>0.596</v>
       </c>
       <c r="J3">
-        <v>0.4507042253521127</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="K3">
-        <v>0.4084507042253521</v>
+        <v>0.3857142857142857</v>
       </c>
       <c r="L3">
-        <v>0.1408450704225352</v>
+        <v>0.1285714285714286</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1011,7 +993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1048,10 +1030,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1065,13 +1047,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1085,10 +1067,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1102,10 +1084,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1119,13 +1101,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1139,10 +1121,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1156,13 +1138,13 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1176,13 +1158,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1196,13 +1178,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1216,13 +1198,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1236,13 +1218,13 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1256,10 +1238,10 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1273,13 +1255,13 @@
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1293,13 +1275,13 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1313,13 +1295,13 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1333,13 +1315,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1353,13 +1335,13 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1373,10 +1355,10 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1390,13 +1372,13 @@
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1410,13 +1392,13 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1430,13 +1412,13 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1450,13 +1432,13 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1470,13 +1452,13 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1490,10 +1472,10 @@
         <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G25" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1507,13 +1489,13 @@
         <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1527,13 +1509,13 @@
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>79</v>
+      </c>
+      <c r="E27" t="s">
+        <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
-      </c>
-      <c r="G27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1547,13 +1529,13 @@
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="E28" t="s">
+        <v>79</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
-      </c>
-      <c r="G28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1567,13 +1549,16 @@
         <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>84</v>
+      </c>
+      <c r="E29" t="s">
+        <v>93</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1587,13 +1572,13 @@
         <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="G30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1606,14 +1591,11 @@
       <c r="C31" t="s">
         <v>51</v>
       </c>
-      <c r="D31" t="s">
-        <v>82</v>
-      </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1627,13 +1609,13 @@
         <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G32" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1646,11 +1628,14 @@
       <c r="C33" t="s">
         <v>53</v>
       </c>
+      <c r="D33" t="s">
+        <v>79</v>
+      </c>
       <c r="F33" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1664,13 +1649,13 @@
         <v>54</v>
       </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1684,13 +1669,13 @@
         <v>55</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1703,11 +1688,14 @@
       <c r="C36" t="s">
         <v>56</v>
       </c>
+      <c r="D36" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" t="s">
+        <v>86</v>
+      </c>
       <c r="F36" t="s">
-        <v>98</v>
-      </c>
-      <c r="G36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1721,13 +1709,13 @@
         <v>57</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G37" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1741,13 +1729,13 @@
         <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G38" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1757,11 +1745,14 @@
       <c r="B39" t="s">
         <v>59</v>
       </c>
-      <c r="E39" t="s">
-        <v>88</v>
+      <c r="C39" t="s">
+        <v>59</v>
       </c>
       <c r="F39" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="G39" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1771,11 +1762,17 @@
       <c r="B40" t="s">
         <v>60</v>
       </c>
-      <c r="E40" t="s">
-        <v>89</v>
+      <c r="C40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" t="s">
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="G40" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1785,11 +1782,17 @@
       <c r="B41" t="s">
         <v>61</v>
       </c>
-      <c r="E41" t="s">
-        <v>90</v>
+      <c r="C41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" t="s">
+        <v>88</v>
       </c>
       <c r="F41" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="G41" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1799,11 +1802,14 @@
       <c r="B42" t="s">
         <v>62</v>
       </c>
-      <c r="E42" t="s">
-        <v>91</v>
+      <c r="C42" t="s">
+        <v>62</v>
       </c>
       <c r="F42" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="G42" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1813,11 +1819,17 @@
       <c r="B43" t="s">
         <v>63</v>
       </c>
-      <c r="E43" t="s">
-        <v>81</v>
+      <c r="C43" t="s">
+        <v>63</v>
+      </c>
+      <c r="D43" t="s">
+        <v>89</v>
       </c>
       <c r="F43" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="G43" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1827,11 +1839,17 @@
       <c r="B44" t="s">
         <v>64</v>
       </c>
-      <c r="E44" t="s">
-        <v>92</v>
+      <c r="C44" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" t="s">
+        <v>77</v>
       </c>
       <c r="F44" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="G44" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1842,10 +1860,10 @@
         <v>65</v>
       </c>
       <c r="E45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F45" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1856,10 +1874,10 @@
         <v>66</v>
       </c>
       <c r="E46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F46" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1870,10 +1888,10 @@
         <v>67</v>
       </c>
       <c r="E47" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F47" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1884,10 +1902,10 @@
         <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F48" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -1898,10 +1916,10 @@
         <v>69</v>
       </c>
       <c r="E49" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F49" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -1912,10 +1930,10 @@
         <v>70</v>
       </c>
       <c r="E50" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F50" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -1926,10 +1944,10 @@
         <v>71</v>
       </c>
       <c r="E51" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="F51" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -1940,10 +1958,10 @@
         <v>72</v>
       </c>
       <c r="E52" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -1954,10 +1972,66 @@
         <v>73</v>
       </c>
       <c r="E53" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="F53" t="s">
-        <v>100</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>74</v>
+      </c>
+      <c r="E54" t="s">
+        <v>101</v>
+      </c>
+      <c r="F54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s">
+        <v>75</v>
+      </c>
+      <c r="E55" t="s">
+        <v>85</v>
+      </c>
+      <c r="F55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>49</v>
+      </c>
+      <c r="E56" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57" t="s">
+        <v>102</v>
+      </c>
+      <c r="F57" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1967,7 +2041,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2004,10 +2078,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2021,13 +2095,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2041,10 +2115,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2058,10 +2132,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2075,13 +2149,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2095,10 +2169,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2112,13 +2186,13 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2132,13 +2206,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2152,13 +2226,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2172,13 +2246,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2186,19 +2260,19 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2206,19 +2280,19 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F13" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2226,16 +2300,16 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F14" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2243,19 +2317,19 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2263,16 +2337,16 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2280,19 +2354,19 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2300,19 +2374,19 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2320,19 +2394,19 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2340,16 +2414,16 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F20" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2357,19 +2431,19 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2377,19 +2451,19 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G22" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2403,10 +2477,10 @@
         <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2420,13 +2494,13 @@
         <v>34</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2440,13 +2514,13 @@
         <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2460,13 +2534,13 @@
         <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F26" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2480,13 +2554,13 @@
         <v>37</v>
       </c>
       <c r="D27" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2494,22 +2568,22 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2517,19 +2591,19 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2537,16 +2611,16 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G30" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2554,22 +2628,22 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" t="s">
         <v>141</v>
       </c>
-      <c r="E31" t="s">
-        <v>145</v>
-      </c>
       <c r="F31" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G31" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2577,16 +2651,16 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F32" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2594,19 +2668,19 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F33" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2614,19 +2688,19 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2634,19 +2708,19 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F35" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2654,16 +2728,16 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G36" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2671,19 +2745,19 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F37" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G37" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2691,19 +2765,19 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G38" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2711,16 +2785,16 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
         <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2728,19 +2802,19 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
         <v>40</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2748,19 +2822,19 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
         <v>41</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E41" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2768,19 +2842,19 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
         <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E42" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2788,19 +2862,19 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
         <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2808,19 +2882,19 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="E44" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F44" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2828,19 +2902,19 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F45" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G45" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2848,16 +2922,16 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C46" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F46" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2865,19 +2939,22 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D47" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" t="s">
         <v>141</v>
       </c>
       <c r="F47" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2885,16 +2962,16 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F48" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G48" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2902,19 +2979,19 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>94</v>
+        <v>100</v>
+      </c>
+      <c r="E49" t="s">
+        <v>100</v>
       </c>
       <c r="F49" t="s">
-        <v>99</v>
-      </c>
-      <c r="G49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2922,19 +2999,19 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D50" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F50" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G50" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2942,19 +3019,19 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2962,16 +3039,16 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G52" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2979,19 +3056,19 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D53" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F53" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G53" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2999,16 +3076,16 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C54" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F54" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G54" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3016,16 +3093,16 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C55" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F55" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G55" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3033,19 +3110,19 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F56" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G56" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3053,19 +3130,19 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C57" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D57" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F57" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G57" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3073,19 +3150,19 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G58" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3093,19 +3170,19 @@
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C59" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D59" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F59" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G59" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3113,19 +3190,19 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C60" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D60" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E60" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F60" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3133,19 +3210,16 @@
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="F61" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G61" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3153,19 +3227,19 @@
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C62" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F62" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G62" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3173,13 +3247,13 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E63" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F63" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3187,13 +3261,13 @@
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E64" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F64" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3201,13 +3275,13 @@
         <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E65" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F65" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -3215,13 +3289,13 @@
         <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E66" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F66" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -3229,13 +3303,13 @@
         <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E67" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F67" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3243,13 +3317,13 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="E68" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F68" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -3257,13 +3331,13 @@
         <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E69" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F69" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3271,13 +3345,13 @@
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E70" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="F70" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -3285,27 +3359,13 @@
         <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="E71" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="F71" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>3</v>
-      </c>
-      <c r="B72" t="s">
-        <v>73</v>
-      </c>
-      <c r="E72" t="s">
-        <v>97</v>
-      </c>
-      <c r="F72" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3352,10 +3412,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3369,13 +3429,13 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3389,10 +3449,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3406,10 +3466,10 @@
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -3423,13 +3483,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3443,10 +3503,10 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -3460,13 +3520,13 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -3480,13 +3540,13 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3500,13 +3560,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3520,13 +3580,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3540,13 +3600,13 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3560,10 +3620,10 @@
         <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -3577,13 +3637,13 @@
         <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3597,13 +3657,13 @@
         <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -3617,13 +3677,13 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -3637,13 +3697,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -3657,13 +3717,13 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -3677,10 +3737,10 @@
         <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G19" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -3694,13 +3754,13 @@
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -3714,13 +3774,13 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3734,13 +3794,13 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -3754,13 +3814,13 @@
         <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E23" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -3774,13 +3834,13 @@
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -3788,16 +3848,16 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G25" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -3805,19 +3865,19 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3825,19 +3885,19 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -3845,19 +3905,19 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E28" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F28" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -3865,19 +3925,19 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E29" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -3885,19 +3945,19 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F30" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -3905,16 +3965,16 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F31" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G31" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -3922,19 +3982,19 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G32" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3942,19 +4002,19 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -3962,19 +4022,19 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -3982,19 +4042,19 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -4002,19 +4062,19 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C36" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -4022,16 +4082,16 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F37" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -4039,19 +4099,19 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C38" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F38" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G38" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -4059,19 +4119,19 @@
         <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G39" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -4079,19 +4139,19 @@
         <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -4099,19 +4159,19 @@
         <v>3</v>
       </c>
       <c r="B41" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G41" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4119,19 +4179,19 @@
         <v>3</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D42" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E42" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -4139,13 +4199,13 @@
         <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E43" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -4153,13 +4213,13 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F44" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -4167,13 +4227,13 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E45" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F45" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -4181,13 +4241,13 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F46" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -4195,13 +4255,13 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F47" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -4209,13 +4269,13 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E48" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F48" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4223,13 +4283,13 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E49" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4237,13 +4297,13 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E50" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F50" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4251,13 +4311,13 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F51" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4265,13 +4325,13 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E52" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F52" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4279,13 +4339,13 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E53" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F53" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -4293,13 +4353,13 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E54" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F54" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -4309,7 +4369,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4352,10 +4412,10 @@
         <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4372,13 +4432,13 @@
         <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4395,10 +4455,10 @@
         <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4415,10 +4475,10 @@
         <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4435,13 +4495,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4458,10 +4518,10 @@
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4478,13 +4538,13 @@
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4501,13 +4561,13 @@
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -4524,13 +4584,13 @@
         <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -4547,13 +4607,13 @@
         <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -4570,13 +4630,13 @@
         <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -4593,10 +4653,10 @@
         <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4613,13 +4673,13 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4636,13 +4696,13 @@
         <v>35</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -4659,13 +4719,13 @@
         <v>36</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -4682,13 +4742,13 @@
         <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -4705,13 +4765,13 @@
         <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4728,10 +4788,10 @@
         <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H19" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4748,13 +4808,13 @@
         <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4771,13 +4831,13 @@
         <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -4794,13 +4854,13 @@
         <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4817,13 +4877,13 @@
         <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F23" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4840,13 +4900,13 @@
         <v>44</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H24" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4863,10 +4923,10 @@
         <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H25" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4883,13 +4943,13 @@
         <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H26" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4906,13 +4966,13 @@
         <v>47</v>
       </c>
       <c r="E27" t="s">
-        <v>76</v>
+        <v>79</v>
+      </c>
+      <c r="F27" t="s">
+        <v>79</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
-      </c>
-      <c r="H27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4929,13 +4989,13 @@
         <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="F28" t="s">
+        <v>79</v>
       </c>
       <c r="G28" t="s">
-        <v>99</v>
-      </c>
-      <c r="H28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4952,13 +5012,16 @@
         <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>84</v>
+      </c>
+      <c r="F29" t="s">
+        <v>93</v>
       </c>
       <c r="G29" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H29" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4975,13 +5038,13 @@
         <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4997,14 +5060,11 @@
       <c r="D31" t="s">
         <v>51</v>
       </c>
-      <c r="E31" t="s">
-        <v>82</v>
-      </c>
       <c r="G31" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -5021,13 +5081,13 @@
         <v>52</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H32" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -5043,11 +5103,14 @@
       <c r="D33" t="s">
         <v>53</v>
       </c>
+      <c r="E33" t="s">
+        <v>79</v>
+      </c>
       <c r="G33" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H33" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -5064,13 +5127,13 @@
         <v>54</v>
       </c>
       <c r="E34" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -5087,13 +5150,13 @@
         <v>55</v>
       </c>
       <c r="E35" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H35" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -5109,11 +5172,14 @@
       <c r="D36" t="s">
         <v>56</v>
       </c>
+      <c r="E36" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" t="s">
+        <v>86</v>
+      </c>
       <c r="G36" t="s">
-        <v>98</v>
-      </c>
-      <c r="H36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -5130,13 +5196,13 @@
         <v>57</v>
       </c>
       <c r="E37" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G37" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H37" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -5153,13 +5219,13 @@
         <v>58</v>
       </c>
       <c r="E38" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H38" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -5172,11 +5238,14 @@
       <c r="C39" t="s">
         <v>59</v>
       </c>
-      <c r="F39" t="s">
-        <v>88</v>
+      <c r="D39" t="s">
+        <v>59</v>
       </c>
       <c r="G39" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="H39" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -5189,11 +5258,17 @@
       <c r="C40" t="s">
         <v>60</v>
       </c>
-      <c r="F40" t="s">
-        <v>89</v>
+      <c r="D40" t="s">
+        <v>60</v>
+      </c>
+      <c r="E40" t="s">
+        <v>77</v>
       </c>
       <c r="G40" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="H40" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -5206,11 +5281,17 @@
       <c r="C41" t="s">
         <v>61</v>
       </c>
-      <c r="F41" t="s">
-        <v>90</v>
+      <c r="D41" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" t="s">
+        <v>88</v>
       </c>
       <c r="G41" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="H41" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -5223,11 +5304,14 @@
       <c r="C42" t="s">
         <v>62</v>
       </c>
-      <c r="F42" t="s">
-        <v>91</v>
+      <c r="D42" t="s">
+        <v>62</v>
       </c>
       <c r="G42" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="H42" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5240,11 +5324,17 @@
       <c r="C43" t="s">
         <v>63</v>
       </c>
-      <c r="F43" t="s">
-        <v>81</v>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>89</v>
       </c>
       <c r="G43" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="H43" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5257,11 +5347,17 @@
       <c r="C44" t="s">
         <v>64</v>
       </c>
-      <c r="F44" t="s">
-        <v>92</v>
+      <c r="D44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" t="s">
+        <v>77</v>
       </c>
       <c r="G44" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="H44" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -5275,10 +5371,10 @@
         <v>65</v>
       </c>
       <c r="F45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G45" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -5292,10 +5388,10 @@
         <v>66</v>
       </c>
       <c r="F46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G46" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -5309,10 +5405,10 @@
         <v>67</v>
       </c>
       <c r="F47" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="G47" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5326,10 +5422,10 @@
         <v>68</v>
       </c>
       <c r="F48" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G48" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -5343,10 +5439,10 @@
         <v>69</v>
       </c>
       <c r="F49" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -5360,10 +5456,10 @@
         <v>70</v>
       </c>
       <c r="F50" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="G50" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -5377,10 +5473,10 @@
         <v>71</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="G51" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -5394,10 +5490,10 @@
         <v>72</v>
       </c>
       <c r="F52" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G52" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -5411,10 +5507,10 @@
         <v>73</v>
       </c>
       <c r="F53" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G53" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -5422,19 +5518,16 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D54" t="s">
-        <v>22</v>
+        <v>74</v>
+      </c>
+      <c r="F54" t="s">
+        <v>101</v>
       </c>
       <c r="G54" t="s">
-        <v>98</v>
-      </c>
-      <c r="H54" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -5442,22 +5535,16 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
-      </c>
-      <c r="D55" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="F55" t="s">
+        <v>85</v>
       </c>
       <c r="G55" t="s">
-        <v>99</v>
-      </c>
-      <c r="H55" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -5465,19 +5552,16 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56" t="s">
-        <v>24</v>
+        <v>49</v>
+      </c>
+      <c r="F56" t="s">
+        <v>93</v>
       </c>
       <c r="G56" t="s">
-        <v>98</v>
-      </c>
-      <c r="H56" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -5485,19 +5569,16 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
-      </c>
-      <c r="D57" t="s">
-        <v>25</v>
+        <v>76</v>
+      </c>
+      <c r="F57" t="s">
+        <v>102</v>
       </c>
       <c r="G57" t="s">
-        <v>98</v>
-      </c>
-      <c r="H57" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5508,19 +5589,16 @@
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D58" t="s">
-        <v>26</v>
-      </c>
-      <c r="E58" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="G58" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H58" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -5531,16 +5609,19 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D59" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+      <c r="E59" t="s">
+        <v>77</v>
       </c>
       <c r="G59" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H59" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5551,19 +5632,16 @@
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D60" t="s">
-        <v>28</v>
-      </c>
-      <c r="E60" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="G60" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H60" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -5574,19 +5652,16 @@
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>29</v>
-      </c>
-      <c r="E61" t="s">
-        <v>76</v>
-      </c>
-      <c r="F61" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="G61" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H61" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -5597,19 +5672,19 @@
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>76</v>
-      </c>
-      <c r="F62" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H62" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -5620,19 +5695,16 @@
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D63" t="s">
-        <v>31</v>
-      </c>
-      <c r="E63" t="s">
-        <v>85</v>
-      </c>
-      <c r="F63" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H63" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -5643,19 +5715,19 @@
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="D64" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E64" t="s">
-        <v>139</v>
-      </c>
-      <c r="F64" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H64" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -5666,19 +5738,19 @@
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="D65" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>140</v>
+        <v>79</v>
+      </c>
+      <c r="F65" t="s">
+        <v>79</v>
       </c>
       <c r="G65" t="s">
-        <v>99</v>
-      </c>
-      <c r="H65" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -5689,16 +5761,19 @@
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>30</v>
+      </c>
+      <c r="E66" t="s">
+        <v>79</v>
+      </c>
+      <c r="F66" t="s">
+        <v>79</v>
       </c>
       <c r="G66" t="s">
-        <v>98</v>
-      </c>
-      <c r="H66" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -5709,19 +5784,19 @@
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="D67" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="E67" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="F67" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -5732,16 +5807,19 @@
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="D68" t="s">
-        <v>105</v>
+        <v>65</v>
+      </c>
+      <c r="E68" t="s">
+        <v>134</v>
+      </c>
+      <c r="F68" t="s">
+        <v>94</v>
       </c>
       <c r="G68" t="s">
-        <v>98</v>
-      </c>
-      <c r="H68" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -5752,19 +5830,19 @@
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E69" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="G69" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H69" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -5775,19 +5853,16 @@
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D70" t="s">
-        <v>107</v>
-      </c>
-      <c r="E70" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="G70" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H70" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -5798,19 +5873,19 @@
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="D71" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="E71" t="s">
-        <v>81</v>
+        <v>136</v>
+      </c>
+      <c r="F71" t="s">
+        <v>95</v>
       </c>
       <c r="G71" t="s">
-        <v>99</v>
-      </c>
-      <c r="H71" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -5821,16 +5896,16 @@
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G72" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H72" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -5841,19 +5916,19 @@
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E73" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G73" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H73" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -5864,19 +5939,19 @@
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E74" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="G74" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H74" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -5887,16 +5962,19 @@
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>33</v>
+        <v>114</v>
+      </c>
+      <c r="E75" t="s">
+        <v>85</v>
       </c>
       <c r="G75" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H75" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -5907,19 +5985,16 @@
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="D76" t="s">
-        <v>34</v>
-      </c>
-      <c r="E76" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="G76" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H76" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -5930,19 +6005,19 @@
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D77" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="E77" t="s">
-        <v>76</v>
-      </c>
-      <c r="F77" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G77" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H77" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -5953,19 +6028,19 @@
         <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="D78" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="E78" t="s">
-        <v>76</v>
-      </c>
-      <c r="F78" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="G78" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H78" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -5976,19 +6051,16 @@
         <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D79" t="s">
-        <v>37</v>
-      </c>
-      <c r="E79" t="s">
-        <v>86</v>
-      </c>
-      <c r="F79" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="G79" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H79" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -5999,22 +6071,19 @@
         <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D80" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>143</v>
-      </c>
-      <c r="F80" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G80" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H80" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -6025,19 +6094,19 @@
         <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="D81" t="s">
-        <v>112</v>
+        <v>35</v>
       </c>
       <c r="E81" t="s">
-        <v>140</v>
+        <v>79</v>
+      </c>
+      <c r="F81" t="s">
+        <v>79</v>
       </c>
       <c r="G81" t="s">
-        <v>99</v>
-      </c>
-      <c r="H81" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -6048,16 +6117,19 @@
         <v>13</v>
       </c>
       <c r="C82" t="s">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="D82" t="s">
-        <v>113</v>
+        <v>36</v>
+      </c>
+      <c r="E82" t="s">
+        <v>79</v>
+      </c>
+      <c r="F82" t="s">
+        <v>79</v>
       </c>
       <c r="G82" t="s">
-        <v>98</v>
-      </c>
-      <c r="H82" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -6068,22 +6140,19 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="D83" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="E83" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="F83" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="G83" t="s">
-        <v>99</v>
-      </c>
-      <c r="H83" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -6094,16 +6163,22 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="D84" t="s">
-        <v>115</v>
+        <v>67</v>
+      </c>
+      <c r="E84" t="s">
+        <v>138</v>
+      </c>
+      <c r="F84" t="s">
+        <v>96</v>
       </c>
       <c r="G84" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H84" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -6114,19 +6189,19 @@
         <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D85" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E85" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="G85" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H85" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -6137,19 +6212,16 @@
         <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D86" t="s">
-        <v>117</v>
-      </c>
-      <c r="E86" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="G86" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H86" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -6160,19 +6232,22 @@
         <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="D87" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="E87" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="F87" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="G87" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H87" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -6183,16 +6258,16 @@
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D88" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G88" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H88" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -6203,19 +6278,19 @@
         <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D89" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E89" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G89" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H89" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -6226,19 +6301,19 @@
         <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="D90" t="s">
-        <v>62</v>
-      </c>
-      <c r="F90" t="s">
-        <v>91</v>
+        <v>123</v>
+      </c>
+      <c r="E90" t="s">
+        <v>137</v>
       </c>
       <c r="G90" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H90" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -6249,16 +6324,19 @@
         <v>13</v>
       </c>
       <c r="C91" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="D91" t="s">
-        <v>39</v>
+        <v>69</v>
+      </c>
+      <c r="E91" t="s">
+        <v>85</v>
+      </c>
+      <c r="F91" t="s">
+        <v>85</v>
       </c>
       <c r="G91" t="s">
-        <v>98</v>
-      </c>
-      <c r="H91" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6269,19 +6347,16 @@
         <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D92" t="s">
-        <v>40</v>
-      </c>
-      <c r="E92" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="G92" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H92" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -6292,19 +6367,19 @@
         <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="D93" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="E93" t="s">
-        <v>76</v>
-      </c>
-      <c r="F93" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G93" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H93" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -6315,19 +6390,19 @@
         <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D94" t="s">
-        <v>42</v>
-      </c>
-      <c r="E94" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F94" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="G94" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H94" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -6338,19 +6413,16 @@
         <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="D95" t="s">
-        <v>43</v>
-      </c>
-      <c r="E95" t="s">
-        <v>96</v>
-      </c>
-      <c r="F95" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="G95" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H95" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -6361,19 +6433,19 @@
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="D96" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E96" t="s">
-        <v>95</v>
-      </c>
-      <c r="F96" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H96" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -6384,19 +6456,19 @@
         <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="D97" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="E97" t="s">
-        <v>140</v>
+        <v>79</v>
+      </c>
+      <c r="F97" t="s">
+        <v>79</v>
       </c>
       <c r="G97" t="s">
-        <v>99</v>
-      </c>
-      <c r="H97" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -6407,16 +6479,19 @@
         <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="D98" t="s">
-        <v>132</v>
+        <v>42</v>
+      </c>
+      <c r="E98" t="s">
+        <v>79</v>
+      </c>
+      <c r="F98" t="s">
+        <v>79</v>
       </c>
       <c r="G98" t="s">
-        <v>98</v>
-      </c>
-      <c r="H98" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -6427,19 +6502,19 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="D99" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="E99" t="s">
-        <v>141</v>
+        <v>92</v>
+      </c>
+      <c r="F99" t="s">
+        <v>92</v>
       </c>
       <c r="G99" t="s">
-        <v>99</v>
-      </c>
-      <c r="H99" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -6450,16 +6525,19 @@
         <v>13</v>
       </c>
       <c r="C100" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="D100" t="s">
-        <v>134</v>
+        <v>71</v>
+      </c>
+      <c r="E100" t="s">
+        <v>139</v>
+      </c>
+      <c r="F100" t="s">
+        <v>99</v>
       </c>
       <c r="G100" t="s">
-        <v>98</v>
-      </c>
-      <c r="H100" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -6473,16 +6551,16 @@
         <v>126</v>
       </c>
       <c r="D101" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="E101" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="G101" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H101" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -6496,16 +6574,13 @@
         <v>127</v>
       </c>
       <c r="D102" t="s">
-        <v>135</v>
-      </c>
-      <c r="E102" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="G102" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H102" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -6516,19 +6591,22 @@
         <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="D103" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="E103" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="F103" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="G103" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H103" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -6539,16 +6617,16 @@
         <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D104" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G104" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H104" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -6559,19 +6637,19 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>72</v>
       </c>
       <c r="E105" t="s">
-        <v>74</v>
+        <v>100</v>
+      </c>
+      <c r="F105" t="s">
+        <v>100</v>
       </c>
       <c r="G105" t="s">
-        <v>99</v>
-      </c>
-      <c r="H105" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -6585,13 +6663,16 @@
         <v>130</v>
       </c>
       <c r="D106" t="s">
-        <v>138</v>
+        <v>130</v>
+      </c>
+      <c r="E106" t="s">
+        <v>137</v>
       </c>
       <c r="G106" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H106" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -6602,16 +6683,19 @@
         <v>13</v>
       </c>
       <c r="C107" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D107" t="s">
-        <v>45</v>
+        <v>73</v>
+      </c>
+      <c r="E107" t="s">
+        <v>85</v>
+      </c>
+      <c r="F107" t="s">
+        <v>85</v>
       </c>
       <c r="G107" t="s">
-        <v>98</v>
-      </c>
-      <c r="H107" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -6622,19 +6706,16 @@
         <v>13</v>
       </c>
       <c r="C108" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
       <c r="D108" t="s">
-        <v>46</v>
-      </c>
-      <c r="E108" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="G108" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H108" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -6645,19 +6726,19 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="D109" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="E109" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="G109" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H109" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -6668,19 +6749,16 @@
         <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="D110" t="s">
-        <v>48</v>
-      </c>
-      <c r="E110" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="G110" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H110" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -6691,19 +6769,16 @@
         <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D111" t="s">
-        <v>49</v>
-      </c>
-      <c r="E111" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="G111" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H111" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -6714,19 +6789,19 @@
         <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D112" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E112" t="s">
-        <v>82</v>
-      </c>
-      <c r="F112" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G112" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H112" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -6737,19 +6812,19 @@
         <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D113" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E113" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="G113" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H113" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6760,19 +6835,19 @@
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D114" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E114" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G114" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H114" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6783,13 +6858,19 @@
         <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>61</v>
-      </c>
-      <c r="F115" t="s">
-        <v>90</v>
+        <v>55</v>
+      </c>
+      <c r="D115" t="s">
+        <v>55</v>
+      </c>
+      <c r="E115" t="s">
+        <v>78</v>
       </c>
       <c r="G115" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="H115" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -6800,13 +6881,19 @@
         <v>13</v>
       </c>
       <c r="C116" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="D116" t="s">
+        <v>56</v>
+      </c>
+      <c r="E116" t="s">
+        <v>86</v>
       </c>
       <c r="F116" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G116" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6817,13 +6904,16 @@
         <v>13</v>
       </c>
       <c r="C117" t="s">
-        <v>64</v>
-      </c>
-      <c r="F117" t="s">
-        <v>92</v>
+        <v>57</v>
+      </c>
+      <c r="D117" t="s">
+        <v>57</v>
       </c>
       <c r="G117" t="s">
-        <v>100</v>
+        <v>103</v>
+      </c>
+      <c r="H117" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6834,13 +6924,19 @@
         <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>65</v>
-      </c>
-      <c r="F118" t="s">
-        <v>93</v>
+        <v>58</v>
+      </c>
+      <c r="D118" t="s">
+        <v>58</v>
+      </c>
+      <c r="E118" t="s">
+        <v>102</v>
       </c>
       <c r="G118" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="H118" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -6851,13 +6947,13 @@
         <v>13</v>
       </c>
       <c r="C119" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F119" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G119" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -6868,13 +6964,13 @@
         <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F120" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="G120" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -6885,13 +6981,13 @@
         <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="F121" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="G121" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6902,13 +6998,13 @@
         <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F122" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="G122" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -6919,13 +7015,13 @@
         <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="F123" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G123" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -6936,13 +7032,13 @@
         <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="F124" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G124" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -6950,19 +7046,16 @@
         <v>3</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>22</v>
-      </c>
-      <c r="D125" t="s">
-        <v>22</v>
+        <v>48</v>
+      </c>
+      <c r="F125" t="s">
+        <v>79</v>
       </c>
       <c r="G125" t="s">
-        <v>98</v>
-      </c>
-      <c r="H125" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -6970,22 +7063,16 @@
         <v>3</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>23</v>
-      </c>
-      <c r="D126" t="s">
-        <v>23</v>
-      </c>
-      <c r="E126" t="s">
-        <v>74</v>
+        <v>49</v>
+      </c>
+      <c r="F126" t="s">
+        <v>93</v>
       </c>
       <c r="G126" t="s">
-        <v>99</v>
-      </c>
-      <c r="H126" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -6993,19 +7080,16 @@
         <v>3</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
-      </c>
-      <c r="D127" t="s">
-        <v>24</v>
+        <v>76</v>
+      </c>
+      <c r="F127" t="s">
+        <v>102</v>
       </c>
       <c r="G127" t="s">
-        <v>98</v>
-      </c>
-      <c r="H127" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -7016,16 +7100,16 @@
         <v>14</v>
       </c>
       <c r="C128" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D128" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G128" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H128" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -7036,19 +7120,19 @@
         <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E129" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G129" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H129" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -7059,16 +7143,16 @@
         <v>14</v>
       </c>
       <c r="C130" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D130" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G130" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H130" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -7079,19 +7163,16 @@
         <v>14</v>
       </c>
       <c r="C131" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D131" t="s">
-        <v>28</v>
-      </c>
-      <c r="E131" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="G131" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H131" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -7102,19 +7183,19 @@
         <v>14</v>
       </c>
       <c r="C132" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D132" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E132" t="s">
-        <v>76</v>
-      </c>
-      <c r="F132" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G132" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H132" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -7125,19 +7206,16 @@
         <v>14</v>
       </c>
       <c r="C133" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D133" t="s">
-        <v>30</v>
-      </c>
-      <c r="E133" t="s">
-        <v>76</v>
-      </c>
-      <c r="F133" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="G133" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H133" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7148,19 +7226,19 @@
         <v>14</v>
       </c>
       <c r="C134" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D134" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E134" t="s">
-        <v>155</v>
-      </c>
-      <c r="F134" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G134" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H134" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -7171,19 +7249,19 @@
         <v>14</v>
       </c>
       <c r="C135" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D135" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E135" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="F135" t="s">
+        <v>79</v>
       </c>
       <c r="G135" t="s">
-        <v>99</v>
-      </c>
-      <c r="H135" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -7194,16 +7272,19 @@
         <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D136" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="E136" t="s">
+        <v>79</v>
+      </c>
+      <c r="F136" t="s">
+        <v>79</v>
       </c>
       <c r="G136" t="s">
-        <v>98</v>
-      </c>
-      <c r="H136" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7214,19 +7295,19 @@
         <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D137" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E137" t="s">
-        <v>74</v>
+        <v>150</v>
+      </c>
+      <c r="F137" t="s">
+        <v>90</v>
       </c>
       <c r="G137" t="s">
-        <v>99</v>
-      </c>
-      <c r="H137" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -7237,19 +7318,19 @@
         <v>14</v>
       </c>
       <c r="C138" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D138" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E138" t="s">
-        <v>76</v>
-      </c>
-      <c r="F138" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G138" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H138" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -7260,19 +7341,16 @@
         <v>14</v>
       </c>
       <c r="C139" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D139" t="s">
-        <v>36</v>
-      </c>
-      <c r="E139" t="s">
-        <v>76</v>
-      </c>
-      <c r="F139" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="G139" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H139" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -7283,19 +7361,19 @@
         <v>14</v>
       </c>
       <c r="C140" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D140" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E140" t="s">
-        <v>79</v>
-      </c>
-      <c r="F140" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G140" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H140" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7306,19 +7384,19 @@
         <v>14</v>
       </c>
       <c r="C141" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D141" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E141" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="F141" t="s">
+        <v>79</v>
       </c>
       <c r="G141" t="s">
-        <v>99</v>
-      </c>
-      <c r="H141" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -7329,16 +7407,19 @@
         <v>14</v>
       </c>
       <c r="C142" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D142" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="E142" t="s">
+        <v>79</v>
+      </c>
+      <c r="F142" t="s">
+        <v>79</v>
       </c>
       <c r="G142" t="s">
-        <v>98</v>
-      </c>
-      <c r="H142" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -7349,19 +7430,19 @@
         <v>14</v>
       </c>
       <c r="C143" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D143" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E143" t="s">
-        <v>74</v>
+        <v>82</v>
+      </c>
+      <c r="F143" t="s">
+        <v>91</v>
       </c>
       <c r="G143" t="s">
-        <v>99</v>
-      </c>
-      <c r="H143" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -7372,19 +7453,19 @@
         <v>14</v>
       </c>
       <c r="C144" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D144" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E144" t="s">
-        <v>76</v>
-      </c>
-      <c r="F144" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G144" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H144" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -7395,19 +7476,16 @@
         <v>14</v>
       </c>
       <c r="C145" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D145" t="s">
-        <v>42</v>
-      </c>
-      <c r="E145" t="s">
-        <v>76</v>
-      </c>
-      <c r="F145" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="G145" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H145" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -7418,19 +7496,19 @@
         <v>14</v>
       </c>
       <c r="C146" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D146" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E146" t="s">
-        <v>80</v>
-      </c>
-      <c r="F146" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G146" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H146" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -7441,19 +7519,19 @@
         <v>14</v>
       </c>
       <c r="C147" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D147" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E147" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="F147" t="s">
+        <v>79</v>
       </c>
       <c r="G147" t="s">
-        <v>99</v>
-      </c>
-      <c r="H147" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -7464,16 +7542,19 @@
         <v>14</v>
       </c>
       <c r="C148" t="s">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="D148" t="s">
-        <v>120</v>
+        <v>42</v>
+      </c>
+      <c r="E148" t="s">
+        <v>79</v>
+      </c>
+      <c r="F148" t="s">
+        <v>79</v>
       </c>
       <c r="G148" t="s">
-        <v>98</v>
-      </c>
-      <c r="H148" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -7484,19 +7565,19 @@
         <v>14</v>
       </c>
       <c r="C149" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="D149" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="E149" t="s">
-        <v>74</v>
+        <v>83</v>
+      </c>
+      <c r="F149" t="s">
+        <v>92</v>
       </c>
       <c r="G149" t="s">
-        <v>99</v>
-      </c>
-      <c r="H149" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -7507,19 +7588,19 @@
         <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D150" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="E150" t="s">
-        <v>76</v>
-      </c>
-      <c r="F150" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G150" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H150" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -7530,19 +7611,16 @@
         <v>14</v>
       </c>
       <c r="C151" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D151" t="s">
-        <v>71</v>
-      </c>
-      <c r="E151" t="s">
-        <v>76</v>
-      </c>
-      <c r="F151" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="G151" t="s">
-        <v>98</v>
+        <v>103</v>
+      </c>
+      <c r="H151" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -7553,19 +7631,19 @@
         <v>14</v>
       </c>
       <c r="C152" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="D152" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="E152" t="s">
-        <v>156</v>
-      </c>
-      <c r="F152" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="G152" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H152" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -7576,19 +7654,19 @@
         <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="D153" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="E153" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="F153" t="s">
+        <v>79</v>
       </c>
       <c r="G153" t="s">
-        <v>99</v>
-      </c>
-      <c r="H153" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -7599,16 +7677,19 @@
         <v>14</v>
       </c>
       <c r="C154" t="s">
-        <v>149</v>
+        <v>48</v>
       </c>
       <c r="D154" t="s">
-        <v>149</v>
+        <v>48</v>
+      </c>
+      <c r="E154" t="s">
+        <v>79</v>
+      </c>
+      <c r="F154" t="s">
+        <v>79</v>
       </c>
       <c r="G154" t="s">
-        <v>98</v>
-      </c>
-      <c r="H154" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -7619,19 +7700,19 @@
         <v>14</v>
       </c>
       <c r="C155" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="D155" t="s">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="E155" t="s">
-        <v>74</v>
+        <v>151</v>
+      </c>
+      <c r="F155" t="s">
+        <v>93</v>
       </c>
       <c r="G155" t="s">
-        <v>99</v>
-      </c>
-      <c r="H155" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -7642,19 +7723,19 @@
         <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="D156" t="s">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="E156" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G156" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H156" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -7665,19 +7746,16 @@
         <v>14</v>
       </c>
       <c r="C157" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D157" t="s">
-        <v>152</v>
-      </c>
-      <c r="E157" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="G157" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H157" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -7688,19 +7766,19 @@
         <v>14</v>
       </c>
       <c r="C158" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D158" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E158" t="s">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="G158" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H158" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -7711,19 +7789,19 @@
         <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D159" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E159" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G159" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H159" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -7734,16 +7812,19 @@
         <v>14</v>
       </c>
       <c r="C160" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="D160" t="s">
-        <v>45</v>
+        <v>147</v>
+      </c>
+      <c r="E160" t="s">
+        <v>79</v>
       </c>
       <c r="G160" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H160" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -7754,19 +7835,19 @@
         <v>14</v>
       </c>
       <c r="C161" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="D161" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="E161" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="G161" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H161" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -7777,19 +7858,19 @@
         <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="D162" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="E162" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G162" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H162" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -7800,19 +7881,16 @@
         <v>14</v>
       </c>
       <c r="C163" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D163" t="s">
-        <v>48</v>
-      </c>
-      <c r="E163" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="G163" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H163" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -7823,19 +7901,19 @@
         <v>14</v>
       </c>
       <c r="C164" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D164" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E164" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G164" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H164" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -7846,19 +7924,19 @@
         <v>14</v>
       </c>
       <c r="C165" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D165" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E165" t="s">
-        <v>82</v>
-      </c>
-      <c r="F165" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G165" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="H165" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -7869,13 +7947,19 @@
         <v>14</v>
       </c>
       <c r="C166" t="s">
-        <v>59</v>
-      </c>
-      <c r="F166" t="s">
-        <v>88</v>
+        <v>54</v>
+      </c>
+      <c r="D166" t="s">
+        <v>54</v>
+      </c>
+      <c r="E166" t="s">
+        <v>85</v>
       </c>
       <c r="G166" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="H166" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -7886,13 +7970,19 @@
         <v>14</v>
       </c>
       <c r="C167" t="s">
-        <v>60</v>
-      </c>
-      <c r="F167" t="s">
-        <v>89</v>
+        <v>55</v>
+      </c>
+      <c r="D167" t="s">
+        <v>55</v>
+      </c>
+      <c r="E167" t="s">
+        <v>78</v>
       </c>
       <c r="G167" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="H167" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -7903,13 +7993,19 @@
         <v>14</v>
       </c>
       <c r="C168" t="s">
-        <v>61</v>
+        <v>56</v>
+      </c>
+      <c r="D168" t="s">
+        <v>56</v>
+      </c>
+      <c r="E168" t="s">
+        <v>86</v>
       </c>
       <c r="F168" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G168" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -7920,13 +8016,13 @@
         <v>14</v>
       </c>
       <c r="C169" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F169" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G169" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -7937,13 +8033,13 @@
         <v>14</v>
       </c>
       <c r="C170" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F170" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G170" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -7954,13 +8050,13 @@
         <v>14</v>
       </c>
       <c r="C171" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F171" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G171" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -7971,13 +8067,13 @@
         <v>14</v>
       </c>
       <c r="C172" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F172" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G172" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -7988,13 +8084,13 @@
         <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F173" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G173" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -8005,13 +8101,13 @@
         <v>14</v>
       </c>
       <c r="C174" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F174" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="G174" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -8022,13 +8118,13 @@
         <v>14</v>
       </c>
       <c r="C175" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F175" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G175" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -8039,13 +8135,13 @@
         <v>14</v>
       </c>
       <c r="C176" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F176" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="G176" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -8059,10 +8155,61 @@
         <v>73</v>
       </c>
       <c r="F177" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="G177" t="s">
-        <v>100</v>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178">
+        <v>3</v>
+      </c>
+      <c r="B178" t="s">
+        <v>14</v>
+      </c>
+      <c r="C178" t="s">
+        <v>74</v>
+      </c>
+      <c r="F178" t="s">
+        <v>101</v>
+      </c>
+      <c r="G178" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179">
+        <v>3</v>
+      </c>
+      <c r="B179" t="s">
+        <v>14</v>
+      </c>
+      <c r="C179" t="s">
+        <v>75</v>
+      </c>
+      <c r="F179" t="s">
+        <v>85</v>
+      </c>
+      <c r="G179" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180">
+        <v>3</v>
+      </c>
+      <c r="B180" t="s">
+        <v>14</v>
+      </c>
+      <c r="C180" t="s">
+        <v>76</v>
+      </c>
+      <c r="F180" t="s">
+        <v>102</v>
+      </c>
+      <c r="G180" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
